--- a/artfynd/A 62060-2025 artfynd.xlsx
+++ b/artfynd/A 62060-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,48 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128223568</v>
+        <v>66364762</v>
       </c>
       <c r="B2" t="n">
-        <v>92794</v>
+        <v>92183</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>65</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Syltsjön, Jmt</t>
+          <t>Syltsjömyren, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>516370</v>
+        <v>516240</v>
       </c>
       <c r="R2" t="n">
-        <v>7022118</v>
+        <v>7022242</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -743,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2017-05-17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2017-05-17</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -757,33 +754,54 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AN2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>1 substratenheter # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Erik Söderhjelm</t>
+          <t>Magnus Johansson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Erik Söderhjelm</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Magnus Johansson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128223577</v>
+        <v>128223559</v>
       </c>
       <c r="B3" t="n">
-        <v>92810</v>
+        <v>93213</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -814,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>516327</v>
+        <v>516418</v>
       </c>
       <c r="R3" t="n">
-        <v>7022222</v>
+        <v>7022095</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,32 +895,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128223593</v>
+        <v>128223577</v>
       </c>
       <c r="B4" t="n">
-        <v>92794</v>
+        <v>93213</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -915,10 +933,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>516313</v>
+        <v>516327</v>
       </c>
       <c r="R4" t="n">
-        <v>7022314</v>
+        <v>7022222</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -978,14 +996,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128223547</v>
+        <v>128223539</v>
       </c>
       <c r="B5" t="n">
-        <v>92794</v>
+        <v>93197</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1016,10 +1034,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>516471</v>
+        <v>516485</v>
       </c>
       <c r="R5" t="n">
-        <v>7022060</v>
+        <v>7022025</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1079,10 +1097,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128223554</v>
+        <v>128223547</v>
       </c>
       <c r="B6" t="n">
-        <v>57716</v>
+        <v>93197</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1090,27 +1108,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1118,10 +1135,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>516476</v>
+        <v>516471</v>
       </c>
       <c r="R6" t="n">
-        <v>7022046</v>
+        <v>7022060</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1156,17 +1173,13 @@
           <t>2025-09-04</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Älder ringhack</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1185,10 +1198,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128223559</v>
+        <v>128223568</v>
       </c>
       <c r="B7" t="n">
-        <v>92810</v>
+        <v>93197</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1196,21 +1209,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1223,10 +1236,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>516418</v>
+        <v>516370</v>
       </c>
       <c r="R7" t="n">
-        <v>7022095</v>
+        <v>7022118</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1286,14 +1299,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128223539</v>
+        <v>128223575</v>
       </c>
       <c r="B8" t="n">
-        <v>92794</v>
+        <v>93197</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1324,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>516485</v>
+        <v>516384</v>
       </c>
       <c r="R8" t="n">
-        <v>7022025</v>
+        <v>7022228</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1387,32 +1400,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128223590</v>
+        <v>128223587</v>
       </c>
       <c r="B9" t="n">
-        <v>92806</v>
+        <v>93197</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1425,10 +1438,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>516295</v>
+        <v>516261</v>
       </c>
       <c r="R9" t="n">
-        <v>7022271</v>
+        <v>7022204</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1488,32 +1501,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128223622</v>
+        <v>128223588</v>
       </c>
       <c r="B10" t="n">
-        <v>92830</v>
+        <v>93197</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5964</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1526,10 +1539,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>516327</v>
+        <v>516298</v>
       </c>
       <c r="R10" t="n">
-        <v>7022327</v>
+        <v>7022255</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1589,14 +1602,14 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128223575</v>
+        <v>128223593</v>
       </c>
       <c r="B11" t="n">
-        <v>92794</v>
+        <v>93197</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1627,10 +1640,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>516384</v>
+        <v>516313</v>
       </c>
       <c r="R11" t="n">
-        <v>7022228</v>
+        <v>7022314</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1690,32 +1703,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128223588</v>
+        <v>128223590</v>
       </c>
       <c r="B12" t="n">
-        <v>92794</v>
+        <v>93209</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1728,10 +1741,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>516298</v>
+        <v>516295</v>
       </c>
       <c r="R12" t="n">
-        <v>7022255</v>
+        <v>7022271</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1788,6 +1801,213 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>128223622</v>
+      </c>
+      <c r="B13" t="n">
+        <v>93233</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Syltsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>516327</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7022327</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Erik Söderhjelm</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Erik Söderhjelm</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>128223554</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Syltsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>516476</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7022046</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Älder ringhack</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Erik Söderhjelm</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Erik Söderhjelm</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 62060-2025 artfynd.xlsx
+++ b/artfynd/A 62060-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AZ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -789,6 +794,11 @@
       <c r="AY2" t="inlineStr">
         <is>
           <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66364762</t>
         </is>
       </c>
     </row>
@@ -892,6 +902,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128223559</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128223577</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1094,6 +1114,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128223539</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1195,6 +1220,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128223547</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1296,6 +1326,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128223568</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1397,6 +1432,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128223575</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1498,6 +1538,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128223587</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1599,6 +1644,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128223588</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1700,6 +1750,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128223593</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1801,6 +1856,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128223590</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1902,6 +1962,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128223622</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2008,8 +2073,28 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128223554</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>